--- a/output/pdf_financials_xlsx/TARG.xlsx
+++ b/output/pdf_financials_xlsx/TARG.xlsx
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.202532</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.5441049999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.1516</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.1516</v>
       </c>
     </row>
     <row r="93">
@@ -2712,7 +2712,7 @@
         <v>-0.015336</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.8366479999999999</v>
+        <v>0.786008</v>
       </c>
     </row>
     <row r="119">
@@ -3352,7 +3352,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -3826,7 +3830,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3862,7 +3870,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4158,7 +4170,11 @@
           <t>Share-based payments reserve 7,8</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.202532</v>
       </c>
@@ -4420,7 +4436,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TARG.xlsx
+++ b/output/pdf_financials_xlsx/TARG.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.020499</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.017959</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009512</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003158</v>
       </c>
     </row>
     <row r="13">
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.696599</v>
+        <v>-0.717098</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.319654</v>
+        <v>-0.337613</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.033056</v>
+        <v>-0.042568</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.051398</v>
+        <v>-1.054556</v>
       </c>
     </row>
     <row r="28">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.696599</v>
+        <v>-0.717098</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.319654</v>
+        <v>-0.337613</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.033056</v>
+        <v>-0.042568</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.051398</v>
+        <v>-1.054556</v>
       </c>
     </row>
     <row r="30">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">

--- a/output/pdf_financials_xlsx/TARG.xlsx
+++ b/output/pdf_financials_xlsx/TARG.xlsx
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.249813</v>
+        <v>0.279991</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.063858</v>
+        <v>0.085106</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.03886</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.322776</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.394624</v>
       </c>
     </row>
     <row r="65">
@@ -1748,7 +1748,7 @@
         <v>0.358426</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.452624</v>
+        <v>0.847248</v>
       </c>
     </row>
     <row r="69">
@@ -4512,7 +4512,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7118,7 +7122,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>0.030178</v>
       </c>
